--- a/data/trans_bre/P16A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,07</t>
+          <t>3,62; 11,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 20,59</t>
+          <t>11,18; 20,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 18,21</t>
+          <t>9,03; 18,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 17,17</t>
+          <t>7,67; 17,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 101,93</t>
+          <t>24,76; 104,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,92; 131,56</t>
+          <t>54,43; 132,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,56; 108,08</t>
+          <t>43,73; 112,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,18; 70,93</t>
+          <t>25,8; 70,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 12,12</t>
+          <t>4,83; 11,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 16,6</t>
+          <t>8,44; 16,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 12,73</t>
+          <t>5,06; 12,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,04; 30,82</t>
+          <t>16,19; 31,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,24; 103,27</t>
+          <t>32,57; 100,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,39; 98,52</t>
+          <t>38,63; 95,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,22; 70,07</t>
+          <t>23,3; 70,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,19; 339,87</t>
+          <t>70,15; 310,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 18,09</t>
+          <t>9,1; 17,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 20,08</t>
+          <t>11,08; 20,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 17,49</t>
+          <t>9,59; 17,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 50,79</t>
+          <t>11,3; 53,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,47; 171,87</t>
+          <t>65,35; 166,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,97; 142,77</t>
+          <t>59,46; 141,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,26; 133,96</t>
+          <t>57,54; 138,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,98; 249,42</t>
+          <t>47,35; 252,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,82</t>
+          <t>6,61; 13,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 22,5</t>
+          <t>14,58; 22,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 17,93</t>
+          <t>9,6; 17,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 17,53</t>
+          <t>5,14; 18,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,9; 89,39</t>
+          <t>36,26; 92,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,68; 138,39</t>
+          <t>72,13; 140,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,5; 94,15</t>
+          <t>40,18; 90,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 76,14</t>
+          <t>20,81; 77,55</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,95</t>
+          <t>8,02; 11,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,91</t>
+          <t>13,61; 17,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,26</t>
+          <t>10,29; 14,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 31,22</t>
+          <t>14,13; 30,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,56; 92,27</t>
+          <t>54,04; 91,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,06; 106,99</t>
+          <t>72,17; 104,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,19; 80,58</t>
+          <t>51,84; 80,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,43; 160,11</t>
+          <t>58,09; 154,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>12,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,4</t>
+          <t>3,56; 11,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 20,55</t>
+          <t>11,16; 20,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 18,51</t>
+          <t>8,77; 18,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 17,12</t>
+          <t>7,4; 16,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,76; 104,3</t>
+          <t>23,46; 101,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,43; 132,78</t>
+          <t>57,01; 133,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,73; 112,5</t>
+          <t>40,6; 112,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,8; 70,19</t>
+          <t>24,47; 66,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21,94</t>
+          <t>17,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>126,15%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,95</t>
+          <t>5,28; 12,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 16,53</t>
+          <t>8,39; 16,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 12,69</t>
+          <t>4,78; 12,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 31,6</t>
+          <t>13,61; 21,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,57; 100,72</t>
+          <t>35,07; 104,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,63; 95,79</t>
+          <t>39,64; 98,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 70,45</t>
+          <t>21,99; 69,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,15; 310,92</t>
+          <t>55,87; 108,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,13</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>117,95%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 17,66</t>
+          <t>9,61; 17,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 20,23</t>
+          <t>10,59; 19,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 17,88</t>
+          <t>8,83; 17,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 53,02</t>
+          <t>9,47; 18,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,35; 166,05</t>
+          <t>66,08; 166,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,46; 141,67</t>
+          <t>57,35; 137,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,54; 138,82</t>
+          <t>53,0; 139,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,35; 252,15</t>
+          <t>38,74; 90,29</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>15,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,74</t>
+          <t>6,49; 13,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 22,6</t>
+          <t>14,45; 22,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,55</t>
+          <t>9,71; 17,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 18,0</t>
+          <t>11,56; 19,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,26; 92,56</t>
+          <t>35,27; 91,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,13; 140,1</t>
+          <t>72,02; 141,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,18; 90,27</t>
+          <t>40,66; 92,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 77,55</t>
+          <t>42,18; 87,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,84</t>
+          <t>7,95; 11,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,61; 17,67</t>
+          <t>13,39; 17,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,47</t>
+          <t>10,18; 14,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,13; 30,31</t>
+          <t>13,22; 17,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,04; 91,16</t>
+          <t>54,29; 88,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,17; 104,2</t>
+          <t>71,9; 104,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,84; 80,0</t>
+          <t>51,61; 81,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,09; 154,29</t>
+          <t>52,97; 76,03</t>
         </is>
       </c>
     </row>
